--- a/UTCUTS/A1_Outputs/reference_works/ModeloSuelo_BAU.xlsx
+++ b/UTCUTS/A1_Outputs/reference_works/ModeloSuelo_BAU.xlsx
@@ -94209,7 +94209,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EA5D044C-BC17-4DF8-9ECA-0DB07D059EDB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EFFEFAA2-8B81-4647-9BEF-9A4840779C36}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
